--- a/output/graficos_nacionales/plot_nacional_serie_p_basica_m_2018.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_p_basica_m_2018.xlsx
@@ -174,7 +174,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 09:18</t>
+    <t xml:space="preserve">2026-10-05 19:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
